--- a/aec/results/강남/multivariable_results.xlsx
+++ b/aec/results/강남/multivariable_results.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>165774941150.4135</v>
+        <v>165774940702.2059</v>
       </c>
       <c r="F10" t="n">
         <v>15.6238</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5.809675456016488e+24</v>
+        <v>5.809675414645115e+24</v>
       </c>
       <c r="F12" t="n">
         <v>32.7998</v>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>21343455.9162</v>
+        <v>21343455.8898</v>
       </c>
       <c r="F13" t="n">
         <v>8.8864</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.427328936678331e+16</v>
+        <v>8.42732889745163e+16</v>
       </c>
       <c r="F16" t="n">
         <v>22.902</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.917432720699173e+45</v>
+        <v>4.917432649232583e+45</v>
       </c>
       <c r="F17" t="n">
         <v>58.2914</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.380891218526021e+116</v>
+        <v>1.38089121035395e+116</v>
       </c>
       <c r="F18" t="n">
         <v>142.1601</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.70870036213227e+205</v>
+        <v>2.708700152839503e+205</v>
       </c>
       <c r="F20" t="n">
         <v>247.7577</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.668905437886126e+43</v>
+        <v>4.668905386346648e+43</v>
       </c>
       <c r="F23" t="n">
         <v>55.8541</v>
@@ -2705,7 +2705,7 @@
         <v>14.2873</v>
       </c>
       <c r="C24" t="n">
-        <v>1602779.8732</v>
+        <v>1602779.8727</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.173192077641967e+37</v>
+        <v>2.173192053178805e+37</v>
       </c>
       <c r="F33" t="n">
         <v>48.1193</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.467624956431399e+36</v>
+        <v>6.467624886002238e+36</v>
       </c>
       <c r="F34" t="n">
         <v>47.531</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6.509718494360902e+16</v>
+        <v>6.509718465642374e+16</v>
       </c>
       <c r="F35" t="n">
         <v>22.8588</v>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.169358210293473e+40</v>
+        <v>1.169358196484945e+40</v>
       </c>
       <c r="F36" t="n">
         <v>51.4132</v>
@@ -3131,7 +3131,7 @@
         <v>21.9004</v>
       </c>
       <c r="C38" t="n">
-        <v>3244947973.7528</v>
+        <v>3244947972.3688</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2.97197638339632e+229</v>
+        <v>2.971975806496113e+229</v>
       </c>
       <c r="F39" t="n">
         <v>276.0284</v>

--- a/aec/results/강남/multivariable_results.xlsx
+++ b/aec/results/강남/multivariable_results.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="C3" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="D3" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5376</v>
+        <v>0.5507</v>
       </c>
       <c r="C4" t="n">
-        <v>0.613</v>
+        <v>0.6358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6338</v>
+        <v>0.6579</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5371</v>
+        <v>0.5502</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6343</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6258</v>
+        <v>0.6502</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.5790e-291</t>
+          <t>7.2680e-291</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.8125</v>
+        <v>20.4337</v>
       </c>
       <c r="C7" t="n">
-        <v>19.0412</v>
+        <v>18.3967</v>
       </c>
       <c r="D7" t="n">
-        <v>18.521</v>
+        <v>17.8295</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.1889</v>
+        <v>15.0485</v>
       </c>
       <c r="C8" t="n">
-        <v>13.6593</v>
+        <v>13.5588</v>
       </c>
       <c r="D8" t="n">
-        <v>13.2755</v>
+        <v>13.196</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15489.82</v>
+        <v>14849.28</v>
       </c>
       <c r="C9" t="n">
-        <v>15190.62</v>
+        <v>14507.89</v>
       </c>
       <c r="D9" t="n">
-        <v>15154.35</v>
+        <v>14463.11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15506.2</v>
+        <v>14865.54</v>
       </c>
       <c r="C10" t="n">
-        <v>15234.3</v>
+        <v>14551.27</v>
       </c>
       <c r="D10" t="n">
-        <v>15361.85</v>
+        <v>14669.16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="C12" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="D12" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="C13" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="D13" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6232</v>
+        <v>0.624</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7198</v>
+        <v>0.72</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7524</v>
+        <v>0.7522</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5914</v>
+        <v>0.5937</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6944</v>
+        <v>0.6922</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7279</v>
+        <v>0.7262</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6558</v>
+        <v>0.6544</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7463</v>
+        <v>0.7451</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7784</v>
+        <v>0.777</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.7120e-03</t>
+          <t>1.2590e-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.9564e-01</t>
+          <t>8.1625e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.1173e-01</t>
+          <t>8.2464e-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0507</v>
+        <v>0.0516</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1541</v>
+        <v>0.1596</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2074</v>
+        <v>0.2145</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1751</v>
+        <v>0.1746</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1629</v>
+        <v>0.1625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1561</v>
+        <v>0.1556</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1861.37</v>
+        <v>1787.8</v>
       </c>
       <c r="C21" t="n">
-        <v>1742.48</v>
+        <v>1668.07</v>
       </c>
       <c r="D21" t="n">
-        <v>1732.23</v>
+        <v>1658.03</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1877.76</v>
+        <v>1804.07</v>
       </c>
       <c r="C22" t="n">
-        <v>1786.17</v>
+        <v>1711.45</v>
       </c>
       <c r="D22" t="n">
-        <v>1939.73</v>
+        <v>1864.08</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -960,23 +960,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.1139</v>
+        <v>109.8381</v>
       </c>
       <c r="C2" t="n">
-        <v>94.1384</v>
+        <v>95.2893</v>
       </c>
       <c r="D2" t="n">
-        <v>122.0895</v>
+        <v>124.3868</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1254</v>
+        <v>7.4175</v>
       </c>
       <c r="F2" t="n">
-        <v>15.173</v>
+        <v>14.808</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.2855e-49</t>
+          <t>1.1873e-46</t>
         </is>
       </c>
     </row>
@@ -987,23 +987,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.4144</v>
+        <v>42.6045</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2911</v>
+        <v>40.5318</v>
       </c>
       <c r="D3" t="n">
-        <v>44.5376</v>
+        <v>44.6772</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0825</v>
+        <v>1.0567</v>
       </c>
       <c r="F3" t="n">
-        <v>39.181</v>
+        <v>40.3175</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.3006e-240</t>
+          <t>2.4386e-247</t>
         </is>
       </c>
     </row>
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.2976</v>
+        <v>-6.6246</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.2647</v>
+        <v>-7.5751</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.3306</v>
+        <v>-5.6742</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4931</v>
+        <v>0.4846</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.7726</v>
+        <v>-13.6707</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.6846e-36</t>
+          <t>2.2980e-40</t>
         </is>
       </c>
     </row>
@@ -1041,23 +1041,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8698</v>
+        <v>3.9566</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1031</v>
+        <v>-3.562</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6366</v>
+        <v>11.4753</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9599</v>
+        <v>3.8333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9874</v>
+        <v>1.0322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.7039e-02</t>
+          <t>3.0214e-01</t>
         </is>
       </c>
     </row>
@@ -1068,23 +1068,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7723</v>
+        <v>-0.8659</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.5248</v>
+        <v>-2.5758</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.8441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8935</v>
+        <v>0.8718</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8643</v>
+        <v>-0.9932</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.8756e-01</t>
+          <t>3.2075e-01</t>
         </is>
       </c>
     </row>
@@ -1095,23 +1095,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0441</v>
+        <v>-1.371</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.4361</v>
+        <v>-2.7261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.348</v>
+        <v>-0.0159</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7097</v>
+        <v>0.6909</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0621</v>
+        <v>-1.9844</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.5052e-01</t>
+          <t>4.7382e-02</t>
         </is>
       </c>
     </row>
@@ -1122,23 +1122,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.3522</v>
+        <v>-4.8868</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.7897</v>
+        <v>-6.3105</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9147</v>
+        <v>-3.4632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7329</v>
+        <v>0.7258</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.5738</v>
+        <v>-6.7328</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.1351e-06</t>
+          <t>2.2962e-11</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1149,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5175</v>
+        <v>5.7831</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.4199</v>
+        <v>-0.9815</v>
       </c>
       <c r="D9" t="n">
-        <v>8.455</v>
+        <v>12.5477</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5371</v>
+        <v>3.4488</v>
       </c>
       <c r="F9" t="n">
-        <v>0.429</v>
+        <v>1.6768</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.6795e-01</t>
+          <t>9.3765e-02</t>
         </is>
       </c>
     </row>
@@ -1176,23 +1176,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.8262</v>
+        <v>0.3467</v>
       </c>
       <c r="C10" t="n">
-        <v>-34.5577</v>
+        <v>-38.0436</v>
       </c>
       <c r="D10" t="n">
-        <v>44.2101</v>
+        <v>38.7369</v>
       </c>
       <c r="E10" t="n">
-        <v>20.0799</v>
+        <v>19.5727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2403</v>
+        <v>0.0177</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.1009e-01</t>
+          <t>9.8587e-01</t>
         </is>
       </c>
     </row>
@@ -1203,23 +1203,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.8173</v>
+        <v>13.1192</v>
       </c>
       <c r="C11" t="n">
-        <v>-6.7159</v>
+        <v>-8.323499999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>36.3505</v>
+        <v>34.5619</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9787</v>
+        <v>10.9322</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3496</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.7731e-01</t>
+          <t>2.3030e-01</t>
         </is>
       </c>
     </row>
@@ -1230,23 +1230,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.2802</v>
+        <v>20.6752</v>
       </c>
       <c r="C12" t="n">
-        <v>-20.0604</v>
+        <v>-17.583</v>
       </c>
       <c r="D12" t="n">
-        <v>58.6208</v>
+        <v>58.9334</v>
       </c>
       <c r="E12" t="n">
-        <v>20.0578</v>
+        <v>19.5054</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9612000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.3657e-01</t>
+          <t>2.8931e-01</t>
         </is>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-7.4276</v>
+        <v>-14.2956</v>
       </c>
       <c r="C13" t="n">
-        <v>-47.0764</v>
+        <v>-52.9631</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2213</v>
+        <v>24.372</v>
       </c>
       <c r="E13" t="n">
-        <v>20.215</v>
+        <v>19.7141</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3674</v>
+        <v>-0.7251</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.1334e-01</t>
+          <t>4.6847e-01</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-17.1596</v>
+        <v>-17.9422</v>
       </c>
       <c r="C14" t="n">
-        <v>-37.6925</v>
+        <v>-38.4383</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3733</v>
+        <v>2.5538</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4687</v>
+        <v>10.4496</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6391</v>
+        <v>-1.717</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.0137e-01</t>
+          <t>8.6164e-02</t>
         </is>
       </c>
     </row>
@@ -1311,23 +1311,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.6618</v>
+        <v>6.0069</v>
       </c>
       <c r="C15" t="n">
-        <v>-21.8259</v>
+        <v>-22.919</v>
       </c>
       <c r="D15" t="n">
-        <v>37.1496</v>
+        <v>34.9328</v>
       </c>
       <c r="E15" t="n">
-        <v>15.0343</v>
+        <v>14.7475</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4073</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.1038e-01</t>
+          <t>6.8383e-01</t>
         </is>
       </c>
     </row>
@@ -1338,23 +1338,23 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.391999999999999</v>
+        <v>6.656</v>
       </c>
       <c r="C16" t="n">
-        <v>-15.989</v>
+        <v>-18.4052</v>
       </c>
       <c r="D16" t="n">
-        <v>34.7731</v>
+        <v>31.7172</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9405</v>
+        <v>12.7771</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7258</v>
+        <v>0.5209</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.6807e-01</t>
+          <t>6.0248e-01</t>
         </is>
       </c>
     </row>
@@ -1365,23 +1365,23 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1176</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>-37.2419</v>
+        <v>-39.3151</v>
       </c>
       <c r="D17" t="n">
-        <v>41.477</v>
+        <v>37.3565</v>
       </c>
       <c r="E17" t="n">
-        <v>20.0674</v>
+        <v>19.545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1055</v>
+        <v>-0.0501</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9.1597e-01</t>
+          <t>9.6004e-01</t>
         </is>
       </c>
     </row>
@@ -1392,23 +1392,23 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.9471</v>
+        <v>21.9454</v>
       </c>
       <c r="C18" t="n">
-        <v>-3.4965</v>
+        <v>-3.1483</v>
       </c>
       <c r="D18" t="n">
-        <v>47.3907</v>
+        <v>47.0391</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9724</v>
+        <v>12.7937</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6918</v>
+        <v>1.7153</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9.0863e-02</t>
+          <t>8.6474e-02</t>
         </is>
       </c>
     </row>
@@ -1419,23 +1419,23 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.6989</v>
+        <v>-3.8755</v>
       </c>
       <c r="C19" t="n">
-        <v>-28.0779</v>
+        <v>-28.9144</v>
       </c>
       <c r="D19" t="n">
-        <v>22.68</v>
+        <v>21.1633</v>
       </c>
       <c r="E19" t="n">
-        <v>12.9395</v>
+        <v>12.7657</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2086</v>
+        <v>-0.3036</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8.3480e-01</t>
+          <t>7.6148e-01</t>
         </is>
       </c>
     </row>
@@ -1446,23 +1446,23 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.5687</v>
+        <v>24.7315</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9112</v>
+        <v>3.19</v>
       </c>
       <c r="D20" t="n">
-        <v>46.2262</v>
+        <v>46.2729</v>
       </c>
       <c r="E20" t="n">
-        <v>11.0421</v>
+        <v>10.9826</v>
       </c>
       <c r="F20" t="n">
-        <v>2.225</v>
+        <v>2.2519</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.6212e-02</t>
+          <t>2.4462e-02</t>
         </is>
       </c>
     </row>
@@ -1473,23 +1473,23 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6589</v>
+        <v>-0.458</v>
       </c>
       <c r="C21" t="n">
-        <v>-12.4672</v>
+        <v>-15.1197</v>
       </c>
       <c r="D21" t="n">
-        <v>15.785</v>
+        <v>14.2036</v>
       </c>
       <c r="E21" t="n">
-        <v>7.2022</v>
+        <v>7.475</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2303</v>
+        <v>-0.0613</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.1786e-01</t>
+          <t>9.5115e-01</t>
         </is>
       </c>
     </row>
@@ -1500,23 +1500,23 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.7689</v>
+        <v>1.8774</v>
       </c>
       <c r="C22" t="n">
-        <v>-14.82</v>
+        <v>-17.307</v>
       </c>
       <c r="D22" t="n">
-        <v>22.3578</v>
+        <v>21.0618</v>
       </c>
       <c r="E22" t="n">
-        <v>9.477600000000001</v>
+        <v>9.780900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3977</v>
+        <v>0.1919</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.9093e-01</t>
+          <t>8.4781e-01</t>
         </is>
       </c>
     </row>
@@ -1527,23 +1527,23 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33.7503</v>
+        <v>34.1999</v>
       </c>
       <c r="C23" t="n">
-        <v>-5.6332</v>
+        <v>-4.1014</v>
       </c>
       <c r="D23" t="n">
-        <v>73.13379999999999</v>
+        <v>72.5012</v>
       </c>
       <c r="E23" t="n">
-        <v>20.0797</v>
+        <v>19.5274</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6808</v>
+        <v>1.7514</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9.2982e-02</t>
+          <t>8.0067e-02</t>
         </is>
       </c>
     </row>
@@ -1554,23 +1554,23 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.568</v>
+        <v>-9.2258</v>
       </c>
       <c r="C24" t="n">
-        <v>-37.0709</v>
+        <v>-38.1708</v>
       </c>
       <c r="D24" t="n">
-        <v>21.9348</v>
+        <v>19.7193</v>
       </c>
       <c r="E24" t="n">
-        <v>15.042</v>
+        <v>14.7572</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5031</v>
+        <v>-0.6252</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.1494e-01</t>
+          <t>5.3195e-01</t>
         </is>
       </c>
     </row>
@@ -1581,23 +1581,23 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.5784</v>
+        <v>-4.5656</v>
       </c>
       <c r="C25" t="n">
-        <v>-15.694</v>
+        <v>-19.2538</v>
       </c>
       <c r="D25" t="n">
-        <v>12.5372</v>
+        <v>10.1226</v>
       </c>
       <c r="E25" t="n">
-        <v>7.1969</v>
+        <v>7.4886</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2193</v>
+        <v>-0.6097</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8.2643e-01</t>
+          <t>5.4216e-01</t>
         </is>
       </c>
     </row>
@@ -1608,23 +1608,23 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-32.3903</v>
+        <v>-32.1274</v>
       </c>
       <c r="C26" t="n">
-        <v>-71.70140000000001</v>
+        <v>-70.3643</v>
       </c>
       <c r="D26" t="n">
-        <v>6.9209</v>
+        <v>6.1095</v>
       </c>
       <c r="E26" t="n">
-        <v>20.0428</v>
+        <v>19.4945</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6161</v>
+        <v>-1.648</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.0627e-01</t>
+          <t>9.9541e-02</t>
         </is>
       </c>
     </row>
@@ -1635,23 +1635,23 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-21.4713</v>
+        <v>-20.74</v>
       </c>
       <c r="C27" t="n">
-        <v>-51.2355</v>
+        <v>-49.8988</v>
       </c>
       <c r="D27" t="n">
-        <v>8.292899999999999</v>
+        <v>8.418900000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>15.1753</v>
+        <v>14.8662</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4149</v>
+        <v>-1.3951</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.5728e-01</t>
+          <t>1.6317e-01</t>
         </is>
       </c>
     </row>
@@ -1662,23 +1662,23 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.3383</v>
+        <v>12.8929</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.4783</v>
+        <v>-6.9162</v>
       </c>
       <c r="D28" t="n">
-        <v>32.1549</v>
+        <v>32.7019</v>
       </c>
       <c r="E28" t="n">
-        <v>10.1035</v>
+        <v>10.0994</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2212</v>
+        <v>1.2766</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.2218e-01</t>
+          <t>2.0192e-01</t>
         </is>
       </c>
     </row>
@@ -1689,23 +1689,23 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.0797</v>
+        <v>-4.6833</v>
       </c>
       <c r="C29" t="n">
-        <v>-18.195</v>
+        <v>-19.3318</v>
       </c>
       <c r="D29" t="n">
-        <v>10.0355</v>
+        <v>9.965199999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>7.1967</v>
+        <v>7.4684</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5669</v>
+        <v>-0.6271</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.7086e-01</t>
+          <t>5.3069e-01</t>
         </is>
       </c>
     </row>
@@ -1716,23 +1716,23 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.8347</v>
+        <v>2.752</v>
       </c>
       <c r="C30" t="n">
-        <v>-16.7218</v>
+        <v>-17.7572</v>
       </c>
       <c r="D30" t="n">
-        <v>24.3912</v>
+        <v>23.2613</v>
       </c>
       <c r="E30" t="n">
-        <v>10.4807</v>
+        <v>10.4564</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3659</v>
+        <v>0.2632</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7.1450e-01</t>
+          <t>7.9244e-01</t>
         </is>
       </c>
     </row>
@@ -1743,23 +1743,23 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.5895</v>
+        <v>1.4436</v>
       </c>
       <c r="C31" t="n">
-        <v>-11.9734</v>
+        <v>-15.6998</v>
       </c>
       <c r="D31" t="n">
-        <v>21.1523</v>
+        <v>18.5869</v>
       </c>
       <c r="E31" t="n">
-        <v>8.444599999999999</v>
+        <v>8.7403</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5435</v>
+        <v>0.1652</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.8687e-01</t>
+          <t>8.6884e-01</t>
         </is>
       </c>
     </row>
@@ -1770,23 +1770,23 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.9879</v>
+        <v>-2.3188</v>
       </c>
       <c r="C32" t="n">
-        <v>-27.493</v>
+        <v>-27.4995</v>
       </c>
       <c r="D32" t="n">
-        <v>23.5173</v>
+        <v>22.8619</v>
       </c>
       <c r="E32" t="n">
-        <v>13.0038</v>
+        <v>12.838</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1529</v>
+        <v>-0.1806</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8.7852e-01</t>
+          <t>8.5669e-01</t>
         </is>
       </c>
     </row>
@@ -1797,23 +1797,23 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.8128</v>
+        <v>4.7078</v>
       </c>
       <c r="C33" t="n">
-        <v>-24.7046</v>
+        <v>-24.2334</v>
       </c>
       <c r="D33" t="n">
-        <v>34.3301</v>
+        <v>33.6491</v>
       </c>
       <c r="E33" t="n">
-        <v>15.0494</v>
+        <v>14.7553</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3198</v>
+        <v>0.3191</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.4916e-01</t>
+          <t>7.4972e-01</t>
         </is>
       </c>
     </row>
@@ -1824,23 +1824,23 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9.866400000000001</v>
+        <v>7.9868</v>
       </c>
       <c r="C34" t="n">
-        <v>-29.4612</v>
+        <v>-30.2779</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1939</v>
+        <v>46.2515</v>
       </c>
       <c r="E34" t="n">
-        <v>20.0512</v>
+        <v>19.5087</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4921</v>
+        <v>0.4094</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.2274e-01</t>
+          <t>6.8230e-01</t>
         </is>
       </c>
     </row>
@@ -1851,23 +1851,23 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.9905</v>
+        <v>24.3266</v>
       </c>
       <c r="C35" t="n">
-        <v>-14.3225</v>
+        <v>-13.925</v>
       </c>
       <c r="D35" t="n">
-        <v>64.3035</v>
+        <v>62.5781</v>
       </c>
       <c r="E35" t="n">
-        <v>20.0437</v>
+        <v>19.502</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2468</v>
+        <v>1.2474</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.1264e-01</t>
+          <t>2.1243e-01</t>
         </is>
       </c>
     </row>
@@ -1878,23 +1878,23 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>43.352</v>
+        <v>43.2313</v>
       </c>
       <c r="C36" t="n">
-        <v>13.8359</v>
+        <v>14.295</v>
       </c>
       <c r="D36" t="n">
-        <v>72.8681</v>
+        <v>72.1675</v>
       </c>
       <c r="E36" t="n">
-        <v>15.0488</v>
+        <v>14.7527</v>
       </c>
       <c r="F36" t="n">
-        <v>2.8808</v>
+        <v>2.9304</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.0169e-03</t>
+          <t>3.4323e-03</t>
         </is>
       </c>
     </row>
@@ -1905,23 +1905,23 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-5.4435</v>
+        <v>-7.2323</v>
       </c>
       <c r="C37" t="n">
-        <v>-19.5389</v>
+        <v>-21.8767</v>
       </c>
       <c r="D37" t="n">
-        <v>8.651999999999999</v>
+        <v>7.412</v>
       </c>
       <c r="E37" t="n">
-        <v>7.1866</v>
+        <v>7.4662</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7574</v>
+        <v>-0.9687</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.4889e-01</t>
+          <t>3.3285e-01</t>
         </is>
       </c>
     </row>
@@ -1932,23 +1932,23 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-44.7209</v>
+        <v>-48.3258</v>
       </c>
       <c r="C38" t="n">
-        <v>-84.1169</v>
+        <v>-86.66630000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-5.3249</v>
+        <v>-9.9854</v>
       </c>
       <c r="E38" t="n">
-        <v>20.0861</v>
+        <v>19.5473</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2265</v>
+        <v>-2.4722</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.6114e-02</t>
+          <t>1.3528e-02</t>
         </is>
       </c>
     </row>
@@ -1959,23 +1959,23 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.0494</v>
+        <v>19.8802</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3155</v>
+        <v>0.1115</v>
       </c>
       <c r="D39" t="n">
-        <v>39.7833</v>
+        <v>39.6489</v>
       </c>
       <c r="E39" t="n">
-        <v>10.0613</v>
+        <v>10.0788</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9927</v>
+        <v>1.9725</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.6452e-02</t>
+          <t>4.8724e-02</t>
         </is>
       </c>
     </row>
@@ -2042,26 +2042,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.4198</v>
+        <v>-1.4103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2418</v>
+        <v>0.2441</v>
       </c>
       <c r="D2" t="n">
-        <v>0.044</v>
+        <v>0.0409</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3296</v>
+        <v>1.4553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8698</v>
+        <v>0.911</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6324</v>
+        <v>-1.5481</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.0260e-01</t>
+          <t>1.2160e-01</t>
         </is>
       </c>
     </row>
@@ -2072,26 +2072,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1574</v>
+        <v>0.141</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1705</v>
+        <v>1.1514</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8612</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5594</v>
+        <v>1.5394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1464</v>
+        <v>0.1482</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0753</v>
+        <v>0.9516</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.8226e-01</t>
+          <t>3.4129e-01</t>
         </is>
       </c>
     </row>
@@ -2102,26 +2102,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.598</v>
+        <v>0.6054</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8185</v>
+        <v>1.832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5782</v>
+        <v>1.5849</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0953</v>
+        <v>2.1176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0723</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>8.271000000000001</v>
+        <v>8.1892</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.3283e-16</t>
+          <t>2.6295e-16</t>
         </is>
       </c>
     </row>
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7764</v>
+        <v>-0.6352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4601</v>
+        <v>0.5298</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1523</v>
+        <v>0.1757</v>
       </c>
       <c r="E5" t="n">
-        <v>1.39</v>
+        <v>1.5979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5642</v>
+        <v>0.5632</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3762</v>
+        <v>-1.1278</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.6876e-01</t>
+          <t>2.5940e-01</t>
         </is>
       </c>
     </row>
@@ -2162,26 +2162,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0149</v>
+        <v>-0.0047</v>
       </c>
       <c r="C6" t="n">
-        <v>1.015</v>
+        <v>0.9954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8005</v>
+        <v>0.7832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2869</v>
+        <v>1.265</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1211</v>
+        <v>0.1223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1229</v>
+        <v>-0.0381</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.0221e-01</t>
+          <t>9.6964e-01</t>
         </is>
       </c>
     </row>
@@ -2192,26 +2192,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0127</v>
+        <v>0.0604</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0128</v>
+        <v>1.0623</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8339</v>
+        <v>0.8761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.23</v>
+        <v>1.2881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1279</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.9821e-01</t>
+          <t>5.3894e-01</t>
         </is>
       </c>
     </row>
@@ -2222,26 +2222,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1762</v>
+        <v>0.2572</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1926</v>
+        <v>1.2932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9724</v>
+        <v>1.0539</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4627</v>
+        <v>1.5869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1042</v>
+        <v>0.1044</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6913</v>
+        <v>2.4629</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.0777e-02</t>
+          <t>1.3780e-02</t>
         </is>
       </c>
     </row>
@@ -2252,26 +2252,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2303</v>
+        <v>-0.3981</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7943</v>
+        <v>0.6716</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2978</v>
+        <v>0.2505</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1183</v>
+        <v>1.8008</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5032</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4602</v>
+        <v>-0.7911</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.4538e-01</t>
+          <t>4.2891e-01</t>
         </is>
       </c>
     </row>
@@ -2282,26 +2282,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4.7883</v>
+        <v>-4.7368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0083</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>165774940702.2059</v>
+        <v>217473871818.365</v>
       </c>
       <c r="F10" t="n">
-        <v>15.6238</v>
+        <v>15.7361</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3065</v>
+        <v>-0.301</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.5925e-01</t>
+          <t>7.6340e-01</t>
         </is>
       </c>
     </row>
@@ -2312,26 +2312,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.7568</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4691</v>
+        <v>0.4717</v>
       </c>
       <c r="D11" t="n">
-        <v>0.028</v>
+        <v>0.0273</v>
       </c>
       <c r="E11" t="n">
-        <v>7.8607</v>
+        <v>8.162699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4381</v>
+        <v>1.4546</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5263</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.9871e-01</t>
+          <t>6.0543e-01</t>
         </is>
       </c>
     </row>
@@ -2342,26 +2342,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-7.2648</v>
+        <v>-7.8568</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5.809675414645115e+24</v>
+        <v>1.699137147922753e+31</v>
       </c>
       <c r="F12" t="n">
-        <v>32.7998</v>
+        <v>40.6982</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2215</v>
+        <v>-0.1931</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.2471e-01</t>
+          <t>8.4692e-01</t>
         </is>
       </c>
     </row>
@@ -2372,26 +2372,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5823</v>
+        <v>0.5655</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>21343455.8898</v>
+        <v>115308986.9962</v>
       </c>
       <c r="F13" t="n">
-        <v>8.8864</v>
+        <v>9.762</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0609</v>
+        <v>-0.0584</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9.5147e-01</t>
+          <t>9.5343e-01</t>
         </is>
       </c>
     </row>
@@ -2402,26 +2402,26 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2851</v>
+        <v>0.1835</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3299</v>
+        <v>1.2015</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1075</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4536</v>
+        <v>16.1555</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2834</v>
+        <v>1.3259</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2222</v>
+        <v>0.1384</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8.2418e-01</t>
+          <t>8.8990e-01</t>
         </is>
       </c>
     </row>
@@ -2432,26 +2432,26 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0412</v>
+        <v>-0.1139</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9597</v>
+        <v>0.8923</v>
       </c>
       <c r="D15" t="n">
-        <v>0.032</v>
+        <v>0.0287</v>
       </c>
       <c r="E15" t="n">
-        <v>28.7818</v>
+        <v>27.6975</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7352</v>
+        <v>1.7527</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0237</v>
+        <v>-0.065</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9.8108e-01</t>
+          <t>9.4818e-01</t>
         </is>
       </c>
     </row>
@@ -2462,26 +2462,26 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-5.9142</v>
+        <v>-5.9779</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0027</v>
+        <v>0.0025</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.42732889745163e+16</v>
+        <v>5.482749553451126e+17</v>
       </c>
       <c r="F16" t="n">
-        <v>22.902</v>
+        <v>23.89</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2582</v>
+        <v>-0.2502</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.9622e-01</t>
+          <t>8.0241e-01</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.039899999999999</v>
+        <v>-9.153</v>
       </c>
       <c r="C17" t="n">
         <v>0.0001</v>
@@ -2501,17 +2501,17 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.917432649232583e+45</v>
+        <v>1.304604097987171e+49</v>
       </c>
       <c r="F17" t="n">
-        <v>58.2914</v>
+        <v>62.3713</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1551</v>
+        <v>-0.1467</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.7676e-01</t>
+          <t>8.8333e-01</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-11.2062</v>
+        <v>-11.9955</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -2531,17 +2531,17 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.38089121035395e+116</v>
+        <v>1.95718576571727e+163</v>
       </c>
       <c r="F18" t="n">
-        <v>142.1601</v>
+        <v>197.9569</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0788</v>
+        <v>-0.0606</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.3717e-01</t>
+          <t>9.5168e-01</t>
         </is>
       </c>
     </row>
@@ -2552,26 +2552,26 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4864</v>
+        <v>-0.5284</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6148</v>
+        <v>0.5895</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0265</v>
+        <v>0.0241</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2604</v>
+        <v>14.3973</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6041</v>
+        <v>1.6304</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3033</v>
+        <v>-0.3241</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.6170e-01</t>
+          <t>7.4584e-01</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-12.5698</v>
+        <v>-13.8853</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2590,18 +2590,20 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>2.708700152839503e+205</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>247.7577</v>
+        <v>427.4985</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0507</v>
+        <v>-0.0325</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.5954e-01</t>
+          <t>9.7409e-01</t>
         </is>
       </c>
     </row>
@@ -2612,26 +2614,26 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3095</v>
+        <v>-0.2883</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7338</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1313</v>
+        <v>0.1242</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1007</v>
+        <v>4.522</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8779</v>
+        <v>0.917</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3525</v>
+        <v>-0.3144</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.2445e-01</t>
+          <t>7.5321e-01</t>
         </is>
       </c>
     </row>
@@ -2642,26 +2644,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.2601</v>
+        <v>-1.1135</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2836</v>
+        <v>0.3284</v>
       </c>
       <c r="D22" t="n">
-        <v>0.026</v>
+        <v>0.0272</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0944</v>
+        <v>3.9711</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2192</v>
+        <v>1.2717</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0335</v>
+        <v>-0.8756</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.0137e-01</t>
+          <t>3.8127e-01</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2674,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-8.9199</v>
+        <v>-9.320499999999999</v>
       </c>
       <c r="C23" t="n">
         <v>0.0001</v>
@@ -2681,17 +2683,17 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.668905386346648e+43</v>
+        <v>9.083629393035032e+51</v>
       </c>
       <c r="F23" t="n">
-        <v>55.8541</v>
+        <v>65.79649999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1597</v>
+        <v>-0.1417</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8.7312e-01</t>
+          <t>8.8735e-01</t>
         </is>
       </c>
     </row>
@@ -2702,10 +2704,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.2873</v>
+        <v>15.0399</v>
       </c>
       <c r="C24" t="n">
-        <v>1602779.8727</v>
+        <v>3402110.5322</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2716,14 +2718,14 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1092.288</v>
+        <v>1620.4455</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0131</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9.8956e-01</t>
+          <t>9.9259e-01</t>
         </is>
       </c>
     </row>
@@ -2734,26 +2736,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3764</v>
+        <v>-0.3897</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6863</v>
+        <v>0.6773</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1227</v>
+        <v>0.1117</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8392</v>
+        <v>4.1082</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8784</v>
+        <v>0.9197</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4285</v>
+        <v>-0.4237</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.6829e-01</t>
+          <t>6.7180e-01</t>
         </is>
       </c>
     </row>
@@ -2764,10 +2766,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.1964</v>
+        <v>11.6828</v>
       </c>
       <c r="C26" t="n">
-        <v>72869.2439</v>
+        <v>118513.8274</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2778,14 +2780,14 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>360.3914</v>
+        <v>484.9425</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0311</v>
+        <v>0.0241</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9.7522e-01</t>
+          <t>9.8078e-01</t>
         </is>
       </c>
     </row>
@@ -2796,26 +2798,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1191</v>
+        <v>1.9836</v>
       </c>
       <c r="C27" t="n">
-        <v>8.323499999999999</v>
+        <v>7.2688</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2504</v>
+        <v>0.218</v>
       </c>
       <c r="E27" t="n">
-        <v>276.7266</v>
+        <v>242.3395</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7878</v>
+        <v>1.7892</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1853</v>
+        <v>1.1087</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.3589e-01</t>
+          <t>2.6758e-01</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2828,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-14.8738</v>
+        <v>-16.2072</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2840,14 +2842,14 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>667.8383</v>
+        <v>1187.4477</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0223</v>
+        <v>-0.0136</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9.8223e-01</t>
+          <t>9.8911e-01</t>
         </is>
       </c>
     </row>
@@ -2858,26 +2860,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1078</v>
+        <v>0.0532</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1139</v>
+        <v>1.0546</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2004</v>
+        <v>0.1756</v>
       </c>
       <c r="E29" t="n">
-        <v>6.1908</v>
+        <v>6.3318</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8751</v>
+        <v>0.9145</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1232</v>
+        <v>0.0581</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9.0193e-01</t>
+          <t>9.5365e-01</t>
         </is>
       </c>
     </row>
@@ -2888,26 +2890,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3348</v>
+        <v>0.3105</v>
       </c>
       <c r="C30" t="n">
-        <v>1.3976</v>
+        <v>1.3641</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1028</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>19.0022</v>
+        <v>19.2611</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3316</v>
+        <v>1.3509</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2514</v>
+        <v>0.2298</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8.0150e-01</t>
+          <t>8.1823e-01</t>
         </is>
       </c>
     </row>
@@ -2918,26 +2920,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8107</v>
+        <v>-0.8307</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4446</v>
+        <v>0.4357</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0516</v>
+        <v>0.0471</v>
       </c>
       <c r="E31" t="n">
-        <v>3.8293</v>
+        <v>4.028</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0987</v>
+        <v>1.1347</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7379</v>
+        <v>-0.7321</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.6060e-01</t>
+          <t>4.6411e-01</t>
         </is>
       </c>
     </row>
@@ -2948,26 +2950,26 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2455</v>
+        <v>-0.3334</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7823</v>
+        <v>0.7165</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0401</v>
+        <v>0.0353</v>
       </c>
       <c r="E32" t="n">
-        <v>15.2729</v>
+        <v>14.532</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5161</v>
+        <v>1.5356</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1619</v>
+        <v>-0.2171</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8.7137e-01</t>
+          <t>8.2814e-01</t>
         </is>
       </c>
     </row>
@@ -2978,26 +2980,26 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-8.340199999999999</v>
+        <v>-8.835900000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.173192053178805e+37</v>
+        <v>8.090970313194803e+45</v>
       </c>
       <c r="F33" t="n">
-        <v>48.1193</v>
+        <v>58.4414</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1733</v>
+        <v>-0.1512</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8.6240e-01</t>
+          <t>8.7982e-01</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3010,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-8.3992</v>
+        <v>-8.588200000000001</v>
       </c>
       <c r="C34" t="n">
         <v>0.0002</v>
@@ -3017,17 +3019,17 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.467624886002238e+36</v>
+        <v>4.168247429080646e+40</v>
       </c>
       <c r="F34" t="n">
-        <v>47.531</v>
+        <v>52.1026</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1767</v>
+        <v>-0.1648</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8.5974e-01</t>
+          <t>8.6908e-01</t>
         </is>
       </c>
     </row>
@@ -3038,26 +3040,26 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-6.0878</v>
+        <v>-6.4234</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0023</v>
+        <v>0.0016</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6.509718465642374e+16</v>
+        <v>1.968356071724979e+19</v>
       </c>
       <c r="F35" t="n">
-        <v>22.8588</v>
+        <v>25.9442</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2663</v>
+        <v>-0.2476</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7.8999e-01</t>
+          <t>8.0446e-01</t>
         </is>
       </c>
     </row>
@@ -3068,26 +3070,26 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-8.508100000000001</v>
+        <v>-9.109500000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.169358196484945e+40</v>
+        <v>9.852496779102026e+50</v>
       </c>
       <c r="F36" t="n">
-        <v>51.4132</v>
+        <v>64.55549999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1655</v>
+        <v>-0.1411</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.6856e-01</t>
+          <t>8.8778e-01</t>
         </is>
       </c>
     </row>
@@ -3098,26 +3100,26 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4042</v>
+        <v>0.3797</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4981</v>
+        <v>1.4618</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2688</v>
+        <v>0.2423</v>
       </c>
       <c r="E37" t="n">
-        <v>8.349299999999999</v>
+        <v>8.818899999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4611</v>
+        <v>0.414</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6.4472e-01</t>
+          <t>6.7885e-01</t>
         </is>
       </c>
     </row>
@@ -3128,10 +3130,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.9004</v>
+        <v>23.8806</v>
       </c>
       <c r="C38" t="n">
-        <v>3244947972.3688</v>
+        <v>23506857561.9763</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3142,14 +3144,14 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13037.9734</v>
+        <v>33203.1824</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0017</v>
+        <v>0.0007</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9.9866e-01</t>
+          <t>9.9943e-01</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3162,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-12.6245</v>
+        <v>-13.572</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3168,18 +3170,20 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
-        <v>2.971975806496113e+229</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>276.0284</v>
+        <v>418.6559</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0457</v>
+        <v>-0.0324</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9.6352e-01</t>
+          <t>9.7414e-01</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3220,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -3226,7 +3230,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6338</v>
+        <v>0.6579</v>
       </c>
     </row>
     <row r="4">
@@ -3236,7 +3240,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6258</v>
+        <v>0.6502</v>
       </c>
     </row>
     <row r="5">
@@ -3246,7 +3250,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.52370000000001</v>
+        <v>84.9935</v>
       </c>
     </row>
     <row r="6">
@@ -3268,7 +3272,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.521</v>
+        <v>17.8295</v>
       </c>
     </row>
     <row r="8">
@@ -3278,7 +3282,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.2755</v>
+        <v>13.196</v>
       </c>
     </row>
     <row r="9">
@@ -3288,7 +3292,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15154.35</v>
+        <v>14463.11</v>
       </c>
     </row>
     <row r="10">
@@ -3298,7 +3302,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15361.85</v>
+        <v>14669.16</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3338,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -3344,7 +3348,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3358,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7524</v>
+        <v>0.7522</v>
       </c>
     </row>
     <row r="5">
@@ -3364,7 +3368,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7279</v>
+        <v>0.7262</v>
       </c>
     </row>
     <row r="6">
@@ -3374,7 +3378,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7784</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="7">
@@ -3384,7 +3388,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.2329</v>
+        <v>4.346</v>
       </c>
     </row>
     <row r="8">
@@ -3395,7 +3399,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.1173e-01</t>
+          <t>8.2464e-01</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3422,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2074</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="11">
@@ -3428,7 +3432,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1561</v>
+        <v>0.1556</v>
       </c>
     </row>
     <row r="12">
@@ -3438,7 +3442,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1732.23</v>
+        <v>1658.03</v>
       </c>
     </row>
     <row r="13">
@@ -3448,7 +3452,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1939.73</v>
+        <v>1864.08</v>
       </c>
     </row>
     <row r="14">
@@ -3519,19 +3523,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.3318</v>
+        <v>104.1797</v>
       </c>
       <c r="C2" t="n">
-        <v>103.0726</v>
+        <v>102.9129</v>
       </c>
       <c r="D2" t="n">
-        <v>105.5909</v>
+        <v>105.4464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.642</v>
+        <v>0.6458</v>
       </c>
       <c r="F2" t="n">
-        <v>162.5164</v>
+        <v>161.3103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3546,23 +3550,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.005</v>
+        <v>46.1164</v>
       </c>
       <c r="C3" t="n">
-        <v>43.9814</v>
+        <v>44.0994</v>
       </c>
       <c r="D3" t="n">
-        <v>48.0286</v>
+        <v>48.1334</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0317</v>
+        <v>1.0283</v>
       </c>
       <c r="F3" t="n">
-        <v>44.5895</v>
+        <v>44.8456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.4736e-290</t>
+          <t>6.2460e-289</t>
         </is>
       </c>
     </row>
@@ -3573,23 +3577,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5.4116</v>
+        <v>-5.5434</v>
       </c>
       <c r="C4" t="n">
-        <v>-6.399</v>
+        <v>-6.5305</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.4243</v>
+        <v>-4.5564</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5034</v>
+        <v>0.5032</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.7504</v>
+        <v>-11.0153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.8491e-26</t>
+          <t>2.7342e-27</t>
         </is>
       </c>
     </row>
@@ -3656,26 +3660,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.1753</v>
+        <v>-1.1895</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3087</v>
+        <v>0.3044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2671</v>
+        <v>0.2622</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3568</v>
+        <v>0.3533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.9075</v>
+        <v>-15.6472</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.6176e-57</t>
+          <t>3.4696e-55</t>
         </is>
       </c>
     </row>
@@ -3686,26 +3690,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9247</v>
+        <v>0.9457</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7338</v>
+        <v>0.7477</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1654</v>
+        <v>1.1961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.118</v>
+        <v>0.1199</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6629</v>
+        <v>-0.4659</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.0742e-01</t>
+          <t>6.4129e-01</t>
         </is>
       </c>
     </row>
@@ -3716,26 +3720,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4604</v>
+        <v>0.4645</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5846</v>
+        <v>1.5913</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4039</v>
+        <v>1.406</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7886</v>
+        <v>1.8009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0618</v>
+        <v>0.0631</v>
       </c>
       <c r="G4" t="n">
-        <v>7.451</v>
+        <v>7.3574</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.2609e-14</t>
+          <t>1.8755e-13</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3776,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -3782,7 +3786,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5376</v>
+        <v>0.5507</v>
       </c>
     </row>
     <row r="4">
@@ -3792,7 +3796,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5371</v>
+        <v>0.5502</v>
       </c>
     </row>
     <row r="5">
@@ -3802,7 +3806,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1008.539</v>
+        <v>1023.4798</v>
       </c>
     </row>
     <row r="6">
@@ -3813,7 +3817,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.5790e-291</t>
+          <t>7.2680e-291</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.8125</v>
+        <v>20.4337</v>
       </c>
     </row>
     <row r="8">
@@ -3834,7 +3838,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.1889</v>
+        <v>15.0485</v>
       </c>
     </row>
     <row r="9">
@@ -3844,7 +3848,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15489.82</v>
+        <v>14849.28</v>
       </c>
     </row>
     <row r="10">
@@ -3854,7 +3858,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15506.2</v>
+        <v>14865.54</v>
       </c>
     </row>
   </sheetData>
@@ -3890,7 +3894,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -3900,7 +3904,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -3910,7 +3914,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6232</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="5">
@@ -3920,7 +3924,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5914</v>
+        <v>0.5937</v>
       </c>
     </row>
     <row r="6">
@@ -3930,7 +3934,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6558</v>
+        <v>0.6544</v>
       </c>
     </row>
     <row r="7">
@@ -3940,7 +3944,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.7525</v>
+        <v>25.5398</v>
       </c>
     </row>
     <row r="8">
@@ -3951,7 +3955,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.7120e-03</t>
+          <t>1.2590e-03</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3978,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0507</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="11">
@@ -3984,7 +3988,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1751</v>
+        <v>0.1746</v>
       </c>
     </row>
     <row r="12">
@@ -3994,7 +3998,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1861.37</v>
+        <v>1787.8</v>
       </c>
     </row>
     <row r="13">
@@ -4004,7 +4008,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1877.76</v>
+        <v>1804.07</v>
       </c>
     </row>
     <row r="14">
@@ -4075,19 +4079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105.3332</v>
+        <v>105.2116</v>
       </c>
       <c r="C2" t="n">
-        <v>104.1232</v>
+        <v>104.0132</v>
       </c>
       <c r="D2" t="n">
-        <v>106.5432</v>
+        <v>106.41</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6169</v>
+        <v>0.611</v>
       </c>
       <c r="F2" t="n">
-        <v>170.7396</v>
+        <v>172.192</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4102,23 +4106,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.4417</v>
+        <v>43.5203</v>
       </c>
       <c r="C3" t="n">
-        <v>41.3656</v>
+        <v>41.4853</v>
       </c>
       <c r="D3" t="n">
-        <v>45.5178</v>
+        <v>45.5552</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0585</v>
+        <v>1.0375</v>
       </c>
       <c r="F3" t="n">
-        <v>41.0398</v>
+        <v>41.9471</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.1062e-257</t>
+          <t>5.0607e-263</t>
         </is>
       </c>
     </row>
@@ -4129,23 +4133,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.3135</v>
+        <v>-6.6477</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.2754</v>
+        <v>-7.5956</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.3517</v>
+        <v>-5.6997</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4904</v>
+        <v>0.4833</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.8742</v>
+        <v>-13.7552</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.7536e-36</t>
+          <t>7.4249e-41</t>
         </is>
       </c>
     </row>
@@ -4156,23 +4160,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.3866</v>
+        <v>3.7075</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.358</v>
+        <v>-3.8052</v>
       </c>
       <c r="D5" t="n">
-        <v>15.1311</v>
+        <v>11.2202</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9486</v>
+        <v>3.8303</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8707</v>
+        <v>0.968</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.1559e-02</t>
+          <t>3.3321e-01</t>
         </is>
       </c>
     </row>
@@ -4183,23 +4187,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.0697</v>
+        <v>-1.4284</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.7762</v>
+        <v>-3.0985</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6367</v>
+        <v>0.2418</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8701</v>
+        <v>0.8515</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2295</v>
+        <v>-1.6774</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.1905e-01</t>
+          <t>9.3647e-02</t>
         </is>
       </c>
     </row>
@@ -4210,23 +4214,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3404</v>
+        <v>-0.9191</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.0477</v>
+        <v>-2.275</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7285</v>
+        <v>0.4367</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7077</v>
+        <v>0.6913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.481</v>
+        <v>-1.3296</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.3061e-01</t>
+          <t>1.8382e-01</t>
         </is>
       </c>
     </row>
@@ -4237,23 +4241,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.0553</v>
+        <v>-4.9021</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.119</v>
+        <v>-5.9653</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9915</v>
+        <v>-3.839</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5424</v>
+        <v>0.542</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.4771</v>
+        <v>-9.043900000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.2011e-13</t>
+          <t>4.0938e-19</t>
         </is>
       </c>
     </row>
@@ -4264,23 +4268,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.0947</v>
+        <v>4.8279</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.8203</v>
+        <v>-1.9213</v>
       </c>
       <c r="D9" t="n">
-        <v>8.0097</v>
+        <v>11.5772</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5257</v>
+        <v>3.441</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3105</v>
+        <v>1.403</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.5623e-01</t>
+          <t>1.6079e-01</t>
         </is>
       </c>
     </row>
@@ -4347,26 +4351,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.3704</v>
+        <v>-1.3782</v>
       </c>
       <c r="C2" t="n">
-        <v>0.254</v>
+        <v>0.252</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2151</v>
+        <v>0.2126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2999</v>
+        <v>0.2988</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0848</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.1562</v>
+        <v>-15.8637</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.0278e-58</t>
+          <t>1.1300e-56</t>
         </is>
       </c>
     </row>
@@ -4377,26 +4381,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0762</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0793</v>
+        <v>1.0792</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8238</v>
+        <v>0.8208</v>
       </c>
       <c r="E3" t="n">
-        <v>1.414</v>
+        <v>1.419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1378</v>
+        <v>0.1396</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5534</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.8002e-01</t>
+          <t>5.8513e-01</t>
         </is>
       </c>
     </row>
@@ -4407,26 +4411,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5797</v>
+        <v>0.5848</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7856</v>
+        <v>1.7946</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5586</v>
+        <v>1.5624</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0455</v>
+        <v>2.0613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0693</v>
+        <v>0.0707</v>
       </c>
       <c r="G4" t="n">
-        <v>8.3596</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.2920e-17</t>
+          <t>1.3288e-16</t>
         </is>
       </c>
     </row>
@@ -4437,26 +4441,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6948</v>
+        <v>-0.5704</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4992</v>
+        <v>0.5653</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1725</v>
+        <v>0.1958</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4444</v>
+        <v>1.632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5421</v>
+        <v>0.541</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2816</v>
+        <v>-1.0545</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.9997e-01</t>
+          <t>2.9165e-01</t>
         </is>
       </c>
     </row>
@@ -4467,26 +4471,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0081</v>
+        <v>0.0013</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0081</v>
+        <v>1.0013</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8062</v>
+        <v>0.7991</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2606</v>
+        <v>1.2545</v>
       </c>
       <c r="F6" t="n">
-        <v>0.114</v>
+        <v>0.1151</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0707</v>
+        <v>0.0109</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.4366e-01</t>
+          <t>9.9132e-01</t>
         </is>
       </c>
     </row>
@@ -4497,26 +4501,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0134</v>
+        <v>0.0333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9867</v>
+        <v>1.0338</v>
       </c>
       <c r="D7" t="n">
-        <v>0.82</v>
+        <v>0.8606</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1873</v>
+        <v>1.2419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0944</v>
+        <v>0.0936</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1422</v>
+        <v>0.3557</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.8692e-01</t>
+          <t>7.2206e-01</t>
         </is>
       </c>
     </row>
@@ -4527,26 +4531,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2726</v>
+        <v>0.3193</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3134</v>
+        <v>1.3762</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1413</v>
+        <v>1.1923</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5114</v>
+        <v>1.5884</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0717</v>
+        <v>0.0732</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8037</v>
+        <v>4.3642</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.4255e-04</t>
+          <t>1.2758e-05</t>
         </is>
       </c>
     </row>
@@ -4557,26 +4561,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1275</v>
+        <v>-0.2588</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8803</v>
+        <v>0.772</v>
       </c>
       <c r="D9" t="n">
-        <v>0.344</v>
+        <v>0.3005</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2524</v>
+        <v>1.9829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4793</v>
+        <v>0.4813</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.266</v>
+        <v>-0.5377</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.9024e-01</t>
+          <t>5.9077e-01</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4617,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -4623,7 +4627,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.613</v>
+        <v>0.6358</v>
       </c>
     </row>
     <row r="4">
@@ -4633,7 +4637,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6343</v>
       </c>
     </row>
     <row r="5">
@@ -4643,7 +4647,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>391.3895</v>
+        <v>415.2786</v>
       </c>
     </row>
     <row r="6">
@@ -4665,7 +4669,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.0412</v>
+        <v>18.3967</v>
       </c>
     </row>
     <row r="8">
@@ -4675,7 +4679,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.6593</v>
+        <v>13.5588</v>
       </c>
     </row>
     <row r="9">
@@ -4685,7 +4689,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15190.62</v>
+        <v>14507.89</v>
       </c>
     </row>
     <row r="10">
@@ -4695,7 +4699,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15234.3</v>
+        <v>14551.27</v>
       </c>
     </row>
   </sheetData>
@@ -4731,7 +4735,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="3">
@@ -4741,7 +4745,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -4751,7 +4755,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7198</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="5">
@@ -4761,7 +4765,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6944</v>
+        <v>0.6922</v>
       </c>
     </row>
     <row r="6">
@@ -4771,7 +4775,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7463</v>
+        <v>0.7451</v>
       </c>
     </row>
     <row r="7">
@@ -4781,7 +4785,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.5815</v>
+        <v>4.4314</v>
       </c>
     </row>
     <row r="8">
@@ -4792,7 +4796,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.9564e-01</t>
+          <t>8.1625e-01</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4819,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1541</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="11">
@@ -4825,7 +4829,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1629</v>
+        <v>0.1625</v>
       </c>
     </row>
     <row r="12">
@@ -4835,7 +4839,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1742.48</v>
+        <v>1668.07</v>
       </c>
     </row>
     <row r="13">
@@ -4845,7 +4849,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1786.17</v>
+        <v>1711.45</v>
       </c>
     </row>
     <row r="14">
